--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/WYOMING_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/WYOMING_2012.xlsx
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C230">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C245">
